--- a/Week_3/Dataset_2.xlsx
+++ b/Week_3/Dataset_2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="54" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>
@@ -154,162 +154,162 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="0">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="C2" s="0">
-        <v>17</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="D2" s="0">
         <v>3500</v>
       </c>
       <c r="E2" s="0">
-        <v>2.3837837837837839</v>
+        <v>2.4552598752598751</v>
       </c>
       <c r="F2" s="0">
-        <v>9.2542753648858085</v>
+        <v>10.468223608974293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="0">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="C3" s="0">
-        <v>19.440000000000001</v>
+        <v>23.329999999999998</v>
       </c>
       <c r="D3" s="0">
         <v>3500</v>
       </c>
       <c r="E3" s="0">
-        <v>2.4552598752598751</v>
+        <v>3.5350678733031673</v>
       </c>
       <c r="F3" s="0">
-        <v>10.468223608974293</v>
+        <v>14.23470826715965</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="0">
-        <v>8.5999999999999996</v>
+        <v>12</v>
       </c>
       <c r="C4" s="0">
-        <v>20</v>
+        <v>26.390000000000001</v>
       </c>
       <c r="D4" s="0">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="E4" s="0">
-        <v>2.2341363102232665</v>
+        <v>2.7272727272727271</v>
       </c>
       <c r="F4" s="0">
-        <v>9.8202951954628741</v>
+        <v>18.85787568601349</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="0">
-        <v>23.329999999999998</v>
+        <v>22</v>
       </c>
       <c r="D5" s="0">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="E5" s="0">
-        <v>3.5350678733031673</v>
+        <v>5.4347826086956523</v>
       </c>
       <c r="F5" s="0">
-        <v>14.23470826715965</v>
+        <v>12.152569225635915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="0">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" s="0">
-        <v>26.390000000000001</v>
+        <v>25</v>
       </c>
       <c r="D6" s="0">
-        <v>3100</v>
+        <v>2000</v>
       </c>
       <c r="E6" s="0">
-        <v>2.7272727272727271</v>
+        <v>5.6818181818181817</v>
       </c>
       <c r="F6" s="0">
-        <v>18.85787568601349</v>
+        <v>15.313535148693363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="0">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7" s="0">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="D7" s="0">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="E7" s="0">
-        <v>5.4347826086956523</v>
+        <v>2.2920997920997919</v>
       </c>
       <c r="F7" s="0">
-        <v>12.152569225635915</v>
+        <v>16.06371584862066</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="0">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="C8" s="0">
-        <v>21</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="D8" s="0">
-        <v>5000</v>
+        <v>4250</v>
       </c>
       <c r="E8" s="0">
-        <v>5.1955357142857128</v>
+        <v>5.5900621118012426</v>
       </c>
       <c r="F8" s="0">
-        <v>8.6713417318403714</v>
+        <v>13.817423247834936</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B9" s="0">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D9" s="0">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E9" s="0">
-        <v>5.6818181818181817</v>
+        <v>2.3044096728307255</v>
       </c>
       <c r="F9" s="0">
-        <v>16.612365533747685</v>
+        <v>14.569215837447084</v>
       </c>
     </row>
     <row r="10">

--- a/Week_3/Dataset_2.xlsx
+++ b/Week_3/Dataset_2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="54" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="110" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>

--- a/Week_3/Dataset_2.xlsx
+++ b/Week_3/Dataset_2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="110" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="124" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>
